--- a/backend/data/financials_by_company/000683.SZ.xlsx
+++ b/backend/data/financials_by_company/000683.SZ.xlsx
@@ -692,648 +692,648 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-31495151.213596</v>
+        <v>-43722628.860025</v>
       </c>
       <c r="C2" t="n">
-        <v>0.155428</v>
+        <v>0.099977</v>
       </c>
       <c r="D2" t="n">
-        <v>5453876810.93</v>
+        <v>8087313642.04</v>
       </c>
       <c r="E2" t="n">
-        <v>-202635310</v>
+        <v>-437328178.09</v>
       </c>
       <c r="F2" t="n">
-        <v>-202635310</v>
+        <v>-437328178.09</v>
       </c>
       <c r="G2" t="n">
-        <v>1811195127.71</v>
+        <v>4947921180.15</v>
       </c>
       <c r="H2" t="n">
-        <v>1482080875.38</v>
+        <v>1092010840.93</v>
       </c>
       <c r="I2" t="n">
-        <v>7836266379.97</v>
+        <v>7120057827.69</v>
       </c>
       <c r="J2" t="n">
-        <v>5251241500.93</v>
+        <v>7649985463.95</v>
       </c>
       <c r="K2" t="n">
-        <v>3769160625.55</v>
+        <v>6557974623.02</v>
       </c>
       <c r="L2" t="n">
-        <v>-377706810.39</v>
+        <v>-207382191.95</v>
       </c>
       <c r="M2" t="n">
-        <v>366660899.83</v>
+        <v>248717907.57</v>
       </c>
       <c r="N2" t="n">
-        <v>42680971.4</v>
+        <v>53440562.6</v>
       </c>
       <c r="O2" t="n">
-        <v>1982335286.496404</v>
+        <v>5341526729.379975</v>
       </c>
       <c r="P2" t="n">
-        <v>1811195127.71</v>
+        <v>4947921180.15</v>
       </c>
       <c r="Q2" t="n">
-        <v>9547937220.66</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
+        <v>8767770804.4</v>
+      </c>
+      <c r="R2" t="n">
+        <v>8911166.34</v>
+      </c>
       <c r="S2" t="n">
-        <v>3602721384.98</v>
+        <v>6643305715.99</v>
       </c>
       <c r="T2" t="n">
-        <v>3696316587</v>
+        <v>3638177338</v>
       </c>
       <c r="U2" t="n">
-        <v>3696316587</v>
+        <v>3638177338</v>
       </c>
       <c r="V2" t="n">
-        <v>0.49</v>
+        <v>1.36</v>
       </c>
       <c r="W2" t="n">
-        <v>0.49</v>
+        <v>1.36</v>
       </c>
       <c r="X2" t="n">
-        <v>1811195127.71</v>
+        <v>4947921180.15</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>1811195127.71</v>
+        <v>4947921180.15</v>
       </c>
       <c r="AA2" t="n">
-        <v>-1062461705.99</v>
+        <v>-730556857.9299999</v>
       </c>
       <c r="AB2" t="n">
-        <v>2873656833.7</v>
+        <v>5678478038.08</v>
       </c>
       <c r="AC2" t="n">
-        <v>2873656833.7</v>
+        <v>5678478038.08</v>
       </c>
       <c r="AD2" t="n">
-        <v>528842892.02</v>
+        <v>630778677.37</v>
       </c>
       <c r="AE2" t="n">
-        <v>3402499725.72</v>
+        <v>6309256715.45</v>
       </c>
       <c r="AF2" t="n">
-        <v>-200221659.26</v>
+        <v>-334088869.23</v>
       </c>
       <c r="AG2" t="n">
-        <v>-129703725.43</v>
+        <v>-285496497.64</v>
       </c>
       <c r="AH2" t="n">
-        <v>4197151.17</v>
+        <v>254961691.8</v>
       </c>
       <c r="AI2" t="n">
-        <v>23090458.82</v>
+        <v>16029617.79</v>
       </c>
       <c r="AJ2" t="n">
-        <v>102416115.44</v>
+        <v>14505188.05</v>
       </c>
       <c r="AK2" t="n">
-        <v>-377706810.39</v>
+        <v>-207382191.95</v>
       </c>
       <c r="AL2" t="n">
-        <v>53726881.96</v>
+        <v>12104846.98</v>
       </c>
       <c r="AM2" t="n">
-        <v>366660899.83</v>
+        <v>248717907.57</v>
       </c>
       <c r="AN2" t="n">
-        <v>42680971.4</v>
+        <v>53440562.6</v>
       </c>
       <c r="AO2" t="n">
-        <v>3715982119.77</v>
+        <v>3377683116.97</v>
       </c>
       <c r="AP2" t="n">
-        <v>1711670840.69</v>
+        <v>1647712976.71</v>
       </c>
       <c r="AQ2" t="n">
-        <v>389050609.35</v>
+        <v>727309431.2</v>
       </c>
       <c r="AR2" t="n">
-        <v>157904070.08</v>
+        <v>116955727.15</v>
       </c>
       <c r="AS2" t="n">
-        <v>157904070.08</v>
+        <v>116955727.15</v>
       </c>
       <c r="AT2" t="n">
-        <v>123945457.01</v>
+        <v>156524456.39</v>
       </c>
       <c r="AU2" t="n">
-        <v>1000295187.31</v>
+        <v>739883592.24</v>
       </c>
       <c r="AV2" t="n">
-        <v>306601890.56</v>
+        <v>117809130.71</v>
       </c>
       <c r="AW2" t="n">
-        <v>693693296.75</v>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+        <v>622074461.53</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>8911166.34</v>
+      </c>
       <c r="AY2" t="n">
-        <v>5427652960.46</v>
+        <v>5025396093.68</v>
       </c>
       <c r="AZ2" t="n">
-        <v>7836266379.97</v>
+        <v>7120057827.69</v>
       </c>
       <c r="BA2" t="n">
-        <v>13263919340.43</v>
+        <v>12145453921.37</v>
       </c>
       <c r="BB2" t="n">
-        <v>13263919340.43</v>
+        <v>12145453921.37</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-12817892.283794</v>
+        <v>-8452681.763062</v>
       </c>
       <c r="C3" t="n">
-        <v>0.191581</v>
+        <v>0.127943</v>
       </c>
       <c r="D3" t="n">
-        <v>4095160261.73</v>
+        <v>4847840847.42</v>
       </c>
       <c r="E3" t="n">
-        <v>-66905892.42</v>
+        <v>-66066239.01</v>
       </c>
       <c r="F3" t="n">
-        <v>-66905892.42</v>
+        <v>-66066239.01</v>
       </c>
       <c r="G3" t="n">
-        <v>1409917321.19</v>
+        <v>2659724877.64</v>
       </c>
       <c r="H3" t="n">
-        <v>1047346025.38</v>
+        <v>879681488.16</v>
       </c>
       <c r="I3" t="n">
-        <v>7094431737.06</v>
+        <v>6506041683.1</v>
       </c>
       <c r="J3" t="n">
-        <v>4028254369.31</v>
+        <v>4781774608.41</v>
       </c>
       <c r="K3" t="n">
-        <v>2980908343.93</v>
+        <v>3902093120.25</v>
       </c>
       <c r="L3" t="n">
-        <v>-314346456.61</v>
+        <v>-154394931.68</v>
       </c>
       <c r="M3" t="n">
-        <v>329026447.72</v>
+        <v>243949237.12</v>
       </c>
       <c r="N3" t="n">
-        <v>73112470.59999999</v>
+        <v>108303023.15</v>
       </c>
       <c r="O3" t="n">
-        <v>1464005321.326206</v>
+        <v>2717338434.886938</v>
       </c>
       <c r="P3" t="n">
-        <v>1409917321.19</v>
+        <v>2659724877.64</v>
       </c>
       <c r="Q3" t="n">
-        <v>8529714644.64</v>
-      </c>
-      <c r="R3" t="inlineStr"/>
+        <v>7858907904.73</v>
+      </c>
+      <c r="R3" t="n">
+        <v>10199791.85</v>
+      </c>
       <c r="S3" t="n">
-        <v>3679754891.3</v>
+        <v>3700301995.54</v>
       </c>
       <c r="T3" t="n">
-        <v>3615172618</v>
+        <v>3643458736</v>
       </c>
       <c r="U3" t="n">
-        <v>3615172618</v>
+        <v>3643458736</v>
       </c>
       <c r="V3" t="n">
-        <v>0.39</v>
+        <v>0.73</v>
       </c>
       <c r="W3" t="n">
-        <v>0.39</v>
+        <v>0.73</v>
       </c>
       <c r="X3" t="n">
-        <v>1409917321.19</v>
+        <v>2659724877.64</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1409917321.19</v>
+        <v>2659724877.64</v>
       </c>
       <c r="AA3" t="n">
-        <v>-733914607.14</v>
+        <v>-530386822.17</v>
       </c>
       <c r="AB3" t="n">
-        <v>2143831928.33</v>
+        <v>3190111699.81</v>
       </c>
       <c r="AC3" t="n">
-        <v>2143831928.33</v>
+        <v>3190111699.81</v>
       </c>
       <c r="AD3" t="n">
-        <v>508049967.88</v>
+        <v>468032183.32</v>
       </c>
       <c r="AE3" t="n">
-        <v>2651881896.21</v>
+        <v>3658143883.13</v>
       </c>
       <c r="AF3" t="n">
-        <v>-1027872995.09</v>
+        <v>-42158112.41</v>
       </c>
       <c r="AG3" t="n">
-        <v>-60301754.77</v>
+        <v>-42561832.12</v>
       </c>
       <c r="AH3" t="n">
-        <v>-208409.63</v>
+        <v>8796649.98</v>
       </c>
       <c r="AI3" t="n">
-        <v>-2706921.89</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>63217086.29</v>
-      </c>
+        <v>33765182.14</v>
+      </c>
+      <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="n">
-        <v>-314346456.61</v>
+        <v>-154394931.68</v>
       </c>
       <c r="AL3" t="n">
-        <v>58432479.49</v>
+        <v>18748717.71</v>
       </c>
       <c r="AM3" t="n">
-        <v>329026447.72</v>
+        <v>243949237.12</v>
       </c>
       <c r="AN3" t="n">
-        <v>73112470.59999999</v>
+        <v>108303023.15</v>
       </c>
       <c r="AO3" t="n">
-        <v>3513849110.18</v>
+        <v>3127598183.95</v>
       </c>
       <c r="AP3" t="n">
-        <v>1435282907.58</v>
+        <v>1352866221.63</v>
       </c>
       <c r="AQ3" t="n">
-        <v>337389711.94</v>
+        <v>378867698.05</v>
       </c>
       <c r="AR3" t="n">
-        <v>122565883.31</v>
+        <v>99599931.66</v>
       </c>
       <c r="AS3" t="n">
-        <v>122565883.31</v>
+        <v>99599931.66</v>
       </c>
       <c r="AT3" t="n">
-        <v>151377959.77</v>
+        <v>163560578.58</v>
       </c>
       <c r="AU3" t="n">
-        <v>521000348.15</v>
+        <v>681543967.9400001</v>
       </c>
       <c r="AV3" t="n">
-        <v>191556952.65</v>
+        <v>124856072.04</v>
       </c>
       <c r="AW3" t="n">
-        <v>329443395.5</v>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+        <v>556687895.9</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>10199791.85</v>
+      </c>
       <c r="AY3" t="n">
-        <v>4949132017.76</v>
+        <v>4480464405.58</v>
       </c>
       <c r="AZ3" t="n">
-        <v>7094431737.06</v>
+        <v>6506041683.1</v>
       </c>
       <c r="BA3" t="n">
-        <v>12043563754.82</v>
+        <v>10986506088.68</v>
       </c>
       <c r="BB3" t="n">
-        <v>12043563754.82</v>
+        <v>10986506088.68</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-8452681.763062</v>
+        <v>-12817892.283794</v>
       </c>
       <c r="C4" t="n">
-        <v>0.127943</v>
+        <v>0.191581</v>
       </c>
       <c r="D4" t="n">
-        <v>4847840847.42</v>
+        <v>4095160261.73</v>
       </c>
       <c r="E4" t="n">
-        <v>-66066239.01</v>
+        <v>-66905892.42</v>
       </c>
       <c r="F4" t="n">
-        <v>-66066239.01</v>
+        <v>-66905892.42</v>
       </c>
       <c r="G4" t="n">
-        <v>2659724877.64</v>
+        <v>1409917321.19</v>
       </c>
       <c r="H4" t="n">
-        <v>879681488.16</v>
+        <v>1047346025.38</v>
       </c>
       <c r="I4" t="n">
-        <v>6506041683.1</v>
+        <v>7094431737.06</v>
       </c>
       <c r="J4" t="n">
-        <v>4781774608.41</v>
+        <v>4028254369.31</v>
       </c>
       <c r="K4" t="n">
-        <v>3902093120.25</v>
+        <v>2980908343.93</v>
       </c>
       <c r="L4" t="n">
-        <v>-154394931.68</v>
+        <v>-314346456.61</v>
       </c>
       <c r="M4" t="n">
-        <v>243949237.12</v>
+        <v>329026447.72</v>
       </c>
       <c r="N4" t="n">
-        <v>108303023.15</v>
+        <v>73112470.59999999</v>
       </c>
       <c r="O4" t="n">
-        <v>2717338434.886938</v>
+        <v>1464005321.326206</v>
       </c>
       <c r="P4" t="n">
-        <v>2659724877.64</v>
+        <v>1409917321.19</v>
       </c>
       <c r="Q4" t="n">
-        <v>7858907904.73</v>
-      </c>
-      <c r="R4" t="n">
-        <v>10199791.85</v>
-      </c>
+        <v>8529714644.64</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>3700301995.54</v>
+        <v>3679754891.3</v>
       </c>
       <c r="T4" t="n">
-        <v>3643458736</v>
+        <v>3615172618</v>
       </c>
       <c r="U4" t="n">
-        <v>3643458736</v>
+        <v>3615172618</v>
       </c>
       <c r="V4" t="n">
-        <v>0.73</v>
+        <v>0.39</v>
       </c>
       <c r="W4" t="n">
-        <v>0.73</v>
+        <v>0.39</v>
       </c>
       <c r="X4" t="n">
-        <v>2659724877.64</v>
+        <v>1409917321.19</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2659724877.64</v>
+        <v>1409917321.19</v>
       </c>
       <c r="AA4" t="n">
-        <v>-530386822.17</v>
+        <v>-733914607.14</v>
       </c>
       <c r="AB4" t="n">
-        <v>3190111699.81</v>
+        <v>2143831928.33</v>
       </c>
       <c r="AC4" t="n">
-        <v>3190111699.81</v>
+        <v>2143831928.33</v>
       </c>
       <c r="AD4" t="n">
-        <v>468032183.32</v>
+        <v>508049967.88</v>
       </c>
       <c r="AE4" t="n">
-        <v>3658143883.13</v>
+        <v>2651881896.21</v>
       </c>
       <c r="AF4" t="n">
-        <v>-42158112.41</v>
+        <v>-1027872995.09</v>
       </c>
       <c r="AG4" t="n">
-        <v>-42561832.12</v>
+        <v>-60301754.77</v>
       </c>
       <c r="AH4" t="n">
-        <v>8796649.98</v>
+        <v>-208409.63</v>
       </c>
       <c r="AI4" t="n">
-        <v>33765182.14</v>
-      </c>
-      <c r="AJ4" t="inlineStr"/>
+        <v>-2706921.89</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>63217086.29</v>
+      </c>
       <c r="AK4" t="n">
-        <v>-154394931.68</v>
+        <v>-314346456.61</v>
       </c>
       <c r="AL4" t="n">
-        <v>18748717.71</v>
+        <v>58432479.49</v>
       </c>
       <c r="AM4" t="n">
-        <v>243949237.12</v>
+        <v>329026447.72</v>
       </c>
       <c r="AN4" t="n">
-        <v>108303023.15</v>
+        <v>73112470.59999999</v>
       </c>
       <c r="AO4" t="n">
-        <v>3127598183.95</v>
+        <v>3513849110.18</v>
       </c>
       <c r="AP4" t="n">
-        <v>1352866221.63</v>
+        <v>1435282907.58</v>
       </c>
       <c r="AQ4" t="n">
-        <v>378867698.05</v>
+        <v>337389711.94</v>
       </c>
       <c r="AR4" t="n">
-        <v>99599931.66</v>
+        <v>122565883.31</v>
       </c>
       <c r="AS4" t="n">
-        <v>99599931.66</v>
+        <v>122565883.31</v>
       </c>
       <c r="AT4" t="n">
-        <v>163560578.58</v>
+        <v>151377959.77</v>
       </c>
       <c r="AU4" t="n">
-        <v>681543967.9400001</v>
+        <v>521000348.15</v>
       </c>
       <c r="AV4" t="n">
-        <v>124856072.04</v>
+        <v>191556952.65</v>
       </c>
       <c r="AW4" t="n">
-        <v>556687895.9</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>10199791.85</v>
-      </c>
+        <v>329443395.5</v>
+      </c>
+      <c r="AX4" t="inlineStr"/>
       <c r="AY4" t="n">
-        <v>4480464405.58</v>
+        <v>4949132017.76</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6506041683.1</v>
+        <v>7094431737.06</v>
       </c>
       <c r="BA4" t="n">
-        <v>10986506088.68</v>
+        <v>12043563754.82</v>
       </c>
       <c r="BB4" t="n">
-        <v>10986506088.68</v>
+        <v>12043563754.82</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-43722628.860025</v>
+        <v>-31495151.213596</v>
       </c>
       <c r="C5" t="n">
-        <v>0.099977</v>
+        <v>0.155428</v>
       </c>
       <c r="D5" t="n">
-        <v>8087313642.04</v>
+        <v>5453876810.93</v>
       </c>
       <c r="E5" t="n">
-        <v>-437328178.09</v>
+        <v>-202635310</v>
       </c>
       <c r="F5" t="n">
-        <v>-437328178.09</v>
+        <v>-202635310</v>
       </c>
       <c r="G5" t="n">
-        <v>4947921180.15</v>
+        <v>1811195127.71</v>
       </c>
       <c r="H5" t="n">
-        <v>1092010840.93</v>
+        <v>1482080875.38</v>
       </c>
       <c r="I5" t="n">
-        <v>7120057827.69</v>
+        <v>7836266379.97</v>
       </c>
       <c r="J5" t="n">
-        <v>7649985463.95</v>
+        <v>5251241500.93</v>
       </c>
       <c r="K5" t="n">
-        <v>6557974623.02</v>
+        <v>3769160625.55</v>
       </c>
       <c r="L5" t="n">
-        <v>-207382191.95</v>
+        <v>-377706810.39</v>
       </c>
       <c r="M5" t="n">
-        <v>248717907.57</v>
+        <v>366660899.83</v>
       </c>
       <c r="N5" t="n">
-        <v>53440562.6</v>
+        <v>42680971.4</v>
       </c>
       <c r="O5" t="n">
-        <v>5341526729.379975</v>
+        <v>1982335286.496404</v>
       </c>
       <c r="P5" t="n">
-        <v>4947921180.15</v>
+        <v>1811195127.71</v>
       </c>
       <c r="Q5" t="n">
-        <v>8767770804.4</v>
-      </c>
-      <c r="R5" t="n">
-        <v>8911166.34</v>
-      </c>
+        <v>9547937220.66</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>6643305715.99</v>
+        <v>3602721384.98</v>
       </c>
       <c r="T5" t="n">
-        <v>3638177338</v>
+        <v>3696316587</v>
       </c>
       <c r="U5" t="n">
-        <v>3638177338</v>
+        <v>3696316587</v>
       </c>
       <c r="V5" t="n">
-        <v>1.36</v>
+        <v>0.49</v>
       </c>
       <c r="W5" t="n">
-        <v>1.36</v>
+        <v>0.49</v>
       </c>
       <c r="X5" t="n">
-        <v>4947921180.15</v>
+        <v>1811195127.71</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>4947921180.15</v>
+        <v>1811195127.71</v>
       </c>
       <c r="AA5" t="n">
-        <v>-730556857.9299999</v>
+        <v>-1062461705.99</v>
       </c>
       <c r="AB5" t="n">
-        <v>5678478038.08</v>
+        <v>2873656833.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>5678478038.08</v>
+        <v>2873656833.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>630778677.37</v>
+        <v>528842892.02</v>
       </c>
       <c r="AE5" t="n">
-        <v>6309256715.45</v>
+        <v>3402499725.72</v>
       </c>
       <c r="AF5" t="n">
-        <v>-334088869.23</v>
+        <v>-200221659.26</v>
       </c>
       <c r="AG5" t="n">
-        <v>-285496497.64</v>
+        <v>-129703725.43</v>
       </c>
       <c r="AH5" t="n">
-        <v>254961691.8</v>
+        <v>4197151.17</v>
       </c>
       <c r="AI5" t="n">
-        <v>16029617.79</v>
+        <v>23090458.82</v>
       </c>
       <c r="AJ5" t="n">
-        <v>14505188.05</v>
+        <v>102416115.44</v>
       </c>
       <c r="AK5" t="n">
-        <v>-207382191.95</v>
+        <v>-377706810.39</v>
       </c>
       <c r="AL5" t="n">
-        <v>12104846.98</v>
+        <v>53726881.96</v>
       </c>
       <c r="AM5" t="n">
-        <v>248717907.57</v>
+        <v>366660899.83</v>
       </c>
       <c r="AN5" t="n">
-        <v>53440562.6</v>
+        <v>42680971.4</v>
       </c>
       <c r="AO5" t="n">
-        <v>3377683116.97</v>
+        <v>3715982119.77</v>
       </c>
       <c r="AP5" t="n">
-        <v>1647712976.71</v>
+        <v>1711670840.69</v>
       </c>
       <c r="AQ5" t="n">
-        <v>727309431.2</v>
+        <v>389050609.35</v>
       </c>
       <c r="AR5" t="n">
-        <v>116955727.15</v>
+        <v>157904070.08</v>
       </c>
       <c r="AS5" t="n">
-        <v>116955727.15</v>
+        <v>157904070.08</v>
       </c>
       <c r="AT5" t="n">
-        <v>156524456.39</v>
+        <v>123945457.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>739883592.24</v>
+        <v>1000295187.31</v>
       </c>
       <c r="AV5" t="n">
-        <v>117809130.71</v>
+        <v>306601890.56</v>
       </c>
       <c r="AW5" t="n">
-        <v>622074461.53</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>8911166.34</v>
-      </c>
+        <v>693693296.75</v>
+      </c>
+      <c r="AX5" t="inlineStr"/>
       <c r="AY5" t="n">
-        <v>5025396093.68</v>
+        <v>5427652960.46</v>
       </c>
       <c r="AZ5" t="n">
-        <v>7120057827.69</v>
+        <v>7836266379.97</v>
       </c>
       <c r="BA5" t="n">
-        <v>12145453921.37</v>
+        <v>13263919340.43</v>
       </c>
       <c r="BB5" t="n">
-        <v>12145453921.37</v>
+        <v>13263919340.43</v>
       </c>
     </row>
   </sheetData>
@@ -1719,874 +1719,874 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>3739176560</v>
+        <v>3673412560</v>
       </c>
       <c r="C2" t="n">
-        <v>3739176560</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1747699863.67</v>
-      </c>
+        <v>3673412560</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>8013882030.19</v>
+        <v>5392885647.83</v>
       </c>
       <c r="F2" t="n">
-        <v>13371061914.14</v>
+        <v>10798439626.08</v>
       </c>
       <c r="G2" t="n">
-        <v>20043174288.58</v>
+        <v>15544432776.39</v>
       </c>
       <c r="H2" t="n">
-        <v>-3370273898.99</v>
+        <v>-1956621059.02</v>
       </c>
       <c r="I2" t="n">
-        <v>13371061914.14</v>
-      </c>
-      <c r="J2" t="n">
-        <v>7659506.28</v>
-      </c>
+        <v>10798439626.08</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>14495690792.46</v>
+        <v>11654198814.4</v>
       </c>
       <c r="L2" t="n">
-        <v>18442519094.59</v>
+        <v>12352398814.4</v>
       </c>
       <c r="M2" t="n">
-        <v>19622258436.42</v>
+        <v>14052327254.27</v>
       </c>
       <c r="N2" t="n">
-        <v>5126567643.96</v>
+        <v>2398128439.87</v>
       </c>
       <c r="O2" t="n">
-        <v>14495690792.46</v>
+        <v>11654198814.4</v>
       </c>
       <c r="P2" t="n">
-        <v>312768360</v>
+        <v>144011354.79</v>
       </c>
       <c r="Q2" t="n">
-        <v>9858647154.799999</v>
+        <v>7929949649.1</v>
       </c>
       <c r="R2" t="n">
-        <v>375641474.73</v>
+        <v>1494061855.4</v>
       </c>
       <c r="S2" t="n">
-        <v>3739176560</v>
+        <v>3673412560</v>
       </c>
       <c r="T2" t="n">
-        <v>3739176560</v>
+        <v>3673412560</v>
       </c>
       <c r="U2" t="n">
-        <v>16253598422.88</v>
+        <v>12022542308.81</v>
       </c>
       <c r="V2" t="n">
-        <v>6340400668.26</v>
+        <v>977528591.2</v>
       </c>
       <c r="W2" t="n">
-        <v>1271540187.25</v>
+        <v>61374987.5</v>
       </c>
       <c r="X2" t="n">
-        <v>1041981625.57</v>
+        <v>143828977.22</v>
       </c>
       <c r="Y2" t="n">
-        <v>60975543.7</v>
+        <v>67102341.77</v>
       </c>
       <c r="Z2" t="n">
-        <v>11415503.33</v>
+        <v>7022284.71</v>
       </c>
       <c r="AA2" t="n">
-        <v>3954487808.41</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>7659506.28</v>
-      </c>
+        <v>698200000</v>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>3946828302.13</v>
+        <v>698200000</v>
       </c>
       <c r="AD2" t="n">
-        <v>9913197754.620001</v>
+        <v>11045013717.61</v>
       </c>
       <c r="AE2" t="n">
-        <v>130595616.84</v>
+        <v>64174144.35</v>
       </c>
       <c r="AF2" t="n">
-        <v>4059394221.78</v>
+        <v>4694685647.83</v>
       </c>
       <c r="AG2" t="n">
-        <v>1600655193.99</v>
+        <v>3192033961.99</v>
       </c>
       <c r="AH2" t="n">
-        <v>4601791023.85</v>
+        <v>5630934171.75</v>
       </c>
       <c r="AI2" t="n">
-        <v>787354040.46</v>
+        <v>2510348411.36</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5184810.48</v>
+        <v>13132245.07</v>
       </c>
       <c r="AK2" t="n">
-        <v>121982504.27</v>
+        <v>230129660.47</v>
       </c>
       <c r="AL2" t="n">
-        <v>3687269668.64</v>
+        <v>2877323854.85</v>
       </c>
       <c r="AM2" t="n">
-        <v>35875856859.3</v>
+        <v>26074869563.08</v>
       </c>
       <c r="AN2" t="n">
-        <v>29332933003.67</v>
+        <v>16986476904.49</v>
       </c>
       <c r="AO2" t="n">
-        <v>869175792.6</v>
+        <v>1233474121.66</v>
       </c>
       <c r="AP2" t="n">
-        <v>391759394.84</v>
+        <v>46281332.08</v>
       </c>
       <c r="AQ2" t="n">
-        <v>97121574.92</v>
+        <v>35194274.66</v>
       </c>
       <c r="AR2" t="n">
-        <v>639478499.64</v>
+        <v>430366608.23</v>
       </c>
       <c r="AS2" t="n">
-        <v>639478499.64</v>
+        <v>430366608.23</v>
       </c>
       <c r="AT2" t="n">
-        <v>4245631676.55</v>
+        <v>2290720357.68</v>
       </c>
       <c r="AU2" t="n">
-        <v>383428384.26</v>
+        <v>251554318.49</v>
       </c>
       <c r="AV2" t="n">
-        <v>1124628878.32</v>
+        <v>855759188.3200001</v>
       </c>
       <c r="AW2" t="n">
-        <v>1121482380.79</v>
+        <v>852612690.79</v>
       </c>
       <c r="AX2" t="n">
         <v>3146497.53</v>
       </c>
       <c r="AY2" t="n">
-        <v>21572279418.16</v>
+        <v>11824640100.94</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-9206708633.1</v>
+        <v>-6358318380.78</v>
       </c>
       <c r="BA2" t="n">
-        <v>30778988051.26</v>
+        <v>18182958481.72</v>
       </c>
       <c r="BB2" t="n">
-        <v>1784263208.99</v>
+        <v>1638316812.44</v>
       </c>
       <c r="BC2" t="n">
-        <v>163865247.86</v>
+        <v>96021390.97</v>
       </c>
       <c r="BD2" t="n">
-        <v>17618908576.86</v>
+        <v>10697438951.55</v>
       </c>
       <c r="BE2" t="n">
-        <v>11211951017.55</v>
+        <v>5751181326.76</v>
       </c>
       <c r="BF2" t="n">
-        <v>6542923855.63</v>
+        <v>9088392658.59</v>
       </c>
       <c r="BG2" t="n">
-        <v>1376306294.79</v>
+        <v>2009339665.15</v>
       </c>
       <c r="BH2" t="n">
-        <v>89049811.15000001</v>
+        <v>98669716.73999999</v>
       </c>
       <c r="BI2" t="n">
-        <v>772352416.08</v>
+        <v>675611266.59</v>
       </c>
       <c r="BJ2" t="n">
         <v>0</v>
       </c>
       <c r="BK2" t="inlineStr"/>
       <c r="BL2" t="n">
-        <v>368374748.49</v>
+        <v>453485762.82</v>
       </c>
       <c r="BM2" t="n">
-        <v>403977667.59</v>
+        <v>222125503.77</v>
       </c>
       <c r="BN2" t="n">
-        <v>289106557.87</v>
+        <v>1341413121.84</v>
       </c>
       <c r="BO2" t="n">
-        <v>50636520.76</v>
+        <v>98170862.67</v>
       </c>
       <c r="BP2" t="n">
-        <v>-4316253.27</v>
+        <v>-10755938.6</v>
       </c>
       <c r="BQ2" t="n">
-        <v>54952774.03</v>
+        <v>108926801.27</v>
       </c>
       <c r="BR2" t="n">
-        <v>3965472254.98</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>165688622.53</v>
-      </c>
+        <v>4865188025.6</v>
+      </c>
+      <c r="BS2" t="inlineStr"/>
       <c r="BT2" t="n">
-        <v>3799783632.45</v>
+        <v>4865188025.6</v>
       </c>
       <c r="BU2" t="n">
-        <v>126983574.34</v>
+        <v>464271754.64</v>
       </c>
       <c r="BV2" t="n">
-        <v>3672800058.11</v>
+        <v>3863639481.92</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>3740218560</v>
+        <v>3621758560</v>
       </c>
       <c r="C3" t="n">
-        <v>3740218560</v>
+        <v>3621758560</v>
       </c>
       <c r="D3" t="n">
-        <v>3234076920.3</v>
+        <v>2695725048.52</v>
       </c>
       <c r="E3" t="n">
-        <v>8163400993.19</v>
+        <v>5224471736.1</v>
       </c>
       <c r="F3" t="n">
-        <v>12532057619.82</v>
+        <v>11794957273.96</v>
       </c>
       <c r="G3" t="n">
-        <v>20287842217.71</v>
+        <v>17288436585.77</v>
       </c>
       <c r="H3" t="n">
-        <v>-1195074396.67</v>
+        <v>-1451735810.16</v>
       </c>
       <c r="I3" t="n">
-        <v>12532057619.82</v>
-      </c>
-      <c r="J3" t="n">
-        <v>11241163.73</v>
-      </c>
+        <v>11794957273.96</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>13485680378.89</v>
+        <v>12530595519.9</v>
       </c>
       <c r="L3" t="n">
-        <v>17827650378.89</v>
+        <v>14615695519.9</v>
       </c>
       <c r="M3" t="n">
-        <v>17930984636.68</v>
+        <v>16719205946.99</v>
       </c>
       <c r="N3" t="n">
-        <v>4445304257.79</v>
+        <v>4188610427.09</v>
       </c>
       <c r="O3" t="n">
-        <v>13485680378.89</v>
-      </c>
-      <c r="P3" t="n">
-        <v>433563600</v>
-      </c>
+        <v>12530595519.9</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>9248093791.01</v>
-      </c>
-      <c r="R3" t="n">
-        <v>315103600</v>
-      </c>
+        <v>8518122119.45</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>3740218560</v>
+        <v>3621758560</v>
       </c>
       <c r="T3" t="n">
-        <v>3740218560</v>
+        <v>3621758560</v>
       </c>
       <c r="U3" t="n">
-        <v>16162978965.07</v>
+        <v>13143013766.98</v>
       </c>
       <c r="V3" t="n">
-        <v>7646951281.79</v>
+        <v>3650602541.43</v>
       </c>
       <c r="W3" t="n">
-        <v>1099979455.37</v>
+        <v>54145887.5</v>
       </c>
       <c r="X3" t="n">
-        <v>2119742641.79</v>
+        <v>1434365672.17</v>
       </c>
       <c r="Y3" t="n">
-        <v>62532187.28</v>
+        <v>69115281.86</v>
       </c>
       <c r="Z3" t="n">
-        <v>11485833.62</v>
+        <v>7875699.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>4353211163.73</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>11241163.73</v>
-      </c>
+        <v>2085100000</v>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>4341970000</v>
+        <v>2085100000</v>
       </c>
       <c r="AD3" t="n">
-        <v>8516027683.28</v>
+        <v>9492411225.549999</v>
       </c>
       <c r="AE3" t="n">
-        <v>47399427.64</v>
+        <v>53816734.49</v>
       </c>
       <c r="AF3" t="n">
-        <v>3810189829.46</v>
+        <v>3139371736.1</v>
       </c>
       <c r="AG3" t="n">
-        <v>2460191838.82</v>
+        <v>2672741065.87</v>
       </c>
       <c r="AH3" t="n">
-        <v>4215783793.21</v>
+        <v>5801996953.64</v>
       </c>
       <c r="AI3" t="n">
-        <v>723294687.84</v>
+        <v>531259611.69</v>
       </c>
       <c r="AJ3" t="n">
-        <v>182900000</v>
+        <v>13485100.94</v>
       </c>
       <c r="AK3" t="n">
-        <v>199715559.25</v>
+        <v>325590890.44</v>
       </c>
       <c r="AL3" t="n">
-        <v>3109873546.12</v>
+        <v>4931661350.57</v>
       </c>
       <c r="AM3" t="n">
-        <v>34093963601.75</v>
+        <v>29862219713.97</v>
       </c>
       <c r="AN3" t="n">
-        <v>26773010315.14</v>
+        <v>21821544298.58</v>
       </c>
       <c r="AO3" t="n">
-        <v>499352770.88</v>
+        <v>960334412.8099999</v>
       </c>
       <c r="AP3" t="n">
-        <v>131464524.68</v>
+        <v>38466581.09</v>
       </c>
       <c r="AQ3" t="n">
-        <v>70468991.26000001</v>
+        <v>56937356.05</v>
       </c>
       <c r="AR3" t="n">
-        <v>703838248.24</v>
+        <v>710145015.51</v>
       </c>
       <c r="AS3" t="n">
-        <v>703838248.24</v>
+        <v>710145015.51</v>
       </c>
       <c r="AT3" t="n">
-        <v>3741783362.09</v>
+        <v>3123975568.85</v>
       </c>
       <c r="AU3" t="n">
-        <v>257746665.63</v>
+        <v>244407427.75</v>
       </c>
       <c r="AV3" t="n">
-        <v>953622759.0700001</v>
+        <v>735638245.9400001</v>
       </c>
       <c r="AW3" t="n">
-        <v>950476261.54</v>
+        <v>732491748.41</v>
       </c>
       <c r="AX3" t="n">
         <v>3146497.53</v>
       </c>
       <c r="AY3" t="n">
-        <v>20379389357.86</v>
+        <v>15951639690.58</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-7856710133.64</v>
+        <v>-6878518566.12</v>
       </c>
       <c r="BA3" t="n">
-        <v>28236099491.5</v>
+        <v>22830158256.7</v>
       </c>
       <c r="BB3" t="n">
-        <v>2106984564</v>
+        <v>6028549536.86</v>
       </c>
       <c r="BC3" t="n">
-        <v>152422529.81</v>
+        <v>108459016.21</v>
       </c>
       <c r="BD3" t="n">
-        <v>14647875009.49</v>
+        <v>10725913228.04</v>
       </c>
       <c r="BE3" t="n">
-        <v>11328817388.2</v>
+        <v>5967236475.59</v>
       </c>
       <c r="BF3" t="n">
-        <v>7320953286.61</v>
+        <v>8040675415.39</v>
       </c>
       <c r="BG3" t="n">
-        <v>1896852030.41</v>
+        <v>3848696516.7</v>
       </c>
       <c r="BH3" t="n">
-        <v>94537977.92</v>
+        <v>130267025.23</v>
       </c>
       <c r="BI3" t="n">
-        <v>534822115</v>
+        <v>776254337.79</v>
       </c>
       <c r="BJ3" t="n">
         <v>0</v>
       </c>
-      <c r="BK3" t="n">
-        <v>11404376.05</v>
-      </c>
+      <c r="BK3" t="inlineStr"/>
       <c r="BL3" t="n">
-        <v>254876882.94</v>
+        <v>474687072.83</v>
       </c>
       <c r="BM3" t="n">
-        <v>268540856.01</v>
+        <v>301567264.96</v>
       </c>
       <c r="BN3" t="n">
-        <v>1166787611.92</v>
+        <v>1094999002.46</v>
       </c>
       <c r="BO3" t="n">
-        <v>59868632.84</v>
+        <v>100123222.04</v>
       </c>
       <c r="BP3" t="n">
-        <v>-10333675.11</v>
+        <v>-10669154.55</v>
       </c>
       <c r="BQ3" t="n">
-        <v>70202307.95</v>
+        <v>110792376.59</v>
       </c>
       <c r="BR3" t="n">
-        <v>3568084918.52</v>
-      </c>
-      <c r="BS3" t="inlineStr"/>
+        <v>2090335311.17</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>28219293.82</v>
+      </c>
       <c r="BT3" t="n">
-        <v>3568084918.52</v>
+        <v>2062116017.35</v>
       </c>
       <c r="BU3" t="n">
-        <v>291845441.27</v>
+        <v>206955072.84</v>
       </c>
       <c r="BV3" t="n">
-        <v>3276239477.25</v>
+        <v>1855160944.51</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>3621758560</v>
+        <v>3740218560</v>
       </c>
       <c r="C4" t="n">
-        <v>3621758560</v>
+        <v>3740218560</v>
       </c>
       <c r="D4" t="n">
-        <v>2695725048.52</v>
+        <v>3234076920.3</v>
       </c>
       <c r="E4" t="n">
-        <v>5224471736.1</v>
+        <v>8163400993.19</v>
       </c>
       <c r="F4" t="n">
-        <v>11794957273.96</v>
+        <v>12532057619.82</v>
       </c>
       <c r="G4" t="n">
-        <v>17288436585.77</v>
+        <v>20287842217.71</v>
       </c>
       <c r="H4" t="n">
-        <v>-1451735810.16</v>
+        <v>-1195074396.67</v>
       </c>
       <c r="I4" t="n">
-        <v>11794957273.96</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
+        <v>12532057619.82</v>
+      </c>
+      <c r="J4" t="n">
+        <v>11241163.73</v>
+      </c>
       <c r="K4" t="n">
-        <v>12530595519.9</v>
+        <v>13485680378.89</v>
       </c>
       <c r="L4" t="n">
-        <v>14615695519.9</v>
+        <v>17827650378.89</v>
       </c>
       <c r="M4" t="n">
-        <v>16719205946.99</v>
+        <v>17930984636.68</v>
       </c>
       <c r="N4" t="n">
-        <v>4188610427.09</v>
+        <v>4445304257.79</v>
       </c>
       <c r="O4" t="n">
-        <v>12530595519.9</v>
-      </c>
-      <c r="P4" t="inlineStr"/>
+        <v>13485680378.89</v>
+      </c>
+      <c r="P4" t="n">
+        <v>433563600</v>
+      </c>
       <c r="Q4" t="n">
-        <v>8518122119.45</v>
-      </c>
-      <c r="R4" t="inlineStr"/>
+        <v>9248093791.01</v>
+      </c>
+      <c r="R4" t="n">
+        <v>315103600</v>
+      </c>
       <c r="S4" t="n">
-        <v>3621758560</v>
+        <v>3740218560</v>
       </c>
       <c r="T4" t="n">
-        <v>3621758560</v>
+        <v>3740218560</v>
       </c>
       <c r="U4" t="n">
-        <v>13143013766.98</v>
+        <v>16162978965.07</v>
       </c>
       <c r="V4" t="n">
-        <v>3650602541.43</v>
+        <v>7646951281.79</v>
       </c>
       <c r="W4" t="n">
-        <v>54145887.5</v>
+        <v>1099979455.37</v>
       </c>
       <c r="X4" t="n">
-        <v>1434365672.17</v>
+        <v>2119742641.79</v>
       </c>
       <c r="Y4" t="n">
-        <v>69115281.86</v>
+        <v>62532187.28</v>
       </c>
       <c r="Z4" t="n">
-        <v>7875699.9</v>
+        <v>11485833.62</v>
       </c>
       <c r="AA4" t="n">
-        <v>2085100000</v>
-      </c>
-      <c r="AB4" t="inlineStr"/>
+        <v>4353211163.73</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>11241163.73</v>
+      </c>
       <c r="AC4" t="n">
-        <v>2085100000</v>
+        <v>4341970000</v>
       </c>
       <c r="AD4" t="n">
-        <v>9492411225.549999</v>
+        <v>8516027683.28</v>
       </c>
       <c r="AE4" t="n">
-        <v>53816734.49</v>
+        <v>47399427.64</v>
       </c>
       <c r="AF4" t="n">
-        <v>3139371736.1</v>
+        <v>3810189829.46</v>
       </c>
       <c r="AG4" t="n">
-        <v>2672741065.87</v>
+        <v>2460191838.82</v>
       </c>
       <c r="AH4" t="n">
-        <v>5801996953.64</v>
+        <v>4215783793.21</v>
       </c>
       <c r="AI4" t="n">
-        <v>531259611.69</v>
+        <v>723294687.84</v>
       </c>
       <c r="AJ4" t="n">
-        <v>13485100.94</v>
+        <v>182900000</v>
       </c>
       <c r="AK4" t="n">
-        <v>325590890.44</v>
+        <v>199715559.25</v>
       </c>
       <c r="AL4" t="n">
-        <v>4931661350.57</v>
+        <v>3109873546.12</v>
       </c>
       <c r="AM4" t="n">
-        <v>29862219713.97</v>
+        <v>34093963601.75</v>
       </c>
       <c r="AN4" t="n">
-        <v>21821544298.58</v>
+        <v>26773010315.14</v>
       </c>
       <c r="AO4" t="n">
-        <v>960334412.8099999</v>
+        <v>499352770.88</v>
       </c>
       <c r="AP4" t="n">
-        <v>38466581.09</v>
+        <v>131464524.68</v>
       </c>
       <c r="AQ4" t="n">
-        <v>56937356.05</v>
+        <v>70468991.26000001</v>
       </c>
       <c r="AR4" t="n">
-        <v>710145015.51</v>
+        <v>703838248.24</v>
       </c>
       <c r="AS4" t="n">
-        <v>710145015.51</v>
+        <v>703838248.24</v>
       </c>
       <c r="AT4" t="n">
-        <v>3123975568.85</v>
+        <v>3741783362.09</v>
       </c>
       <c r="AU4" t="n">
-        <v>244407427.75</v>
+        <v>257746665.63</v>
       </c>
       <c r="AV4" t="n">
-        <v>735638245.9400001</v>
+        <v>953622759.0700001</v>
       </c>
       <c r="AW4" t="n">
-        <v>732491748.41</v>
+        <v>950476261.54</v>
       </c>
       <c r="AX4" t="n">
         <v>3146497.53</v>
       </c>
       <c r="AY4" t="n">
-        <v>15951639690.58</v>
+        <v>20379389357.86</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-6878518566.12</v>
+        <v>-7856710133.64</v>
       </c>
       <c r="BA4" t="n">
-        <v>22830158256.7</v>
+        <v>28236099491.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>6028549536.86</v>
+        <v>2106984564</v>
       </c>
       <c r="BC4" t="n">
-        <v>108459016.21</v>
+        <v>152422529.81</v>
       </c>
       <c r="BD4" t="n">
-        <v>10725913228.04</v>
+        <v>14647875009.49</v>
       </c>
       <c r="BE4" t="n">
-        <v>5967236475.59</v>
+        <v>11328817388.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>8040675415.39</v>
+        <v>7320953286.61</v>
       </c>
       <c r="BG4" t="n">
-        <v>3848696516.7</v>
+        <v>1896852030.41</v>
       </c>
       <c r="BH4" t="n">
-        <v>130267025.23</v>
+        <v>94537977.92</v>
       </c>
       <c r="BI4" t="n">
-        <v>776254337.79</v>
+        <v>534822115</v>
       </c>
       <c r="BJ4" t="n">
         <v>0</v>
       </c>
-      <c r="BK4" t="inlineStr"/>
+      <c r="BK4" t="n">
+        <v>11404376.05</v>
+      </c>
       <c r="BL4" t="n">
-        <v>474687072.83</v>
+        <v>254876882.94</v>
       </c>
       <c r="BM4" t="n">
-        <v>301567264.96</v>
+        <v>268540856.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>1094999002.46</v>
+        <v>1166787611.92</v>
       </c>
       <c r="BO4" t="n">
-        <v>100123222.04</v>
+        <v>59868632.84</v>
       </c>
       <c r="BP4" t="n">
-        <v>-10669154.55</v>
+        <v>-10333675.11</v>
       </c>
       <c r="BQ4" t="n">
-        <v>110792376.59</v>
+        <v>70202307.95</v>
       </c>
       <c r="BR4" t="n">
-        <v>2090335311.17</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>28219293.82</v>
-      </c>
+        <v>3568084918.52</v>
+      </c>
+      <c r="BS4" t="inlineStr"/>
       <c r="BT4" t="n">
-        <v>2062116017.35</v>
+        <v>3568084918.52</v>
       </c>
       <c r="BU4" t="n">
-        <v>206955072.84</v>
+        <v>291845441.27</v>
       </c>
       <c r="BV4" t="n">
-        <v>1855160944.51</v>
+        <v>3276239477.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>3673412560</v>
+        <v>3739176560</v>
       </c>
       <c r="C5" t="n">
-        <v>3673412560</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
+        <v>3739176560</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1747699863.67</v>
+      </c>
       <c r="E5" t="n">
-        <v>5392885647.83</v>
+        <v>8013882030.19</v>
       </c>
       <c r="F5" t="n">
-        <v>10798439626.08</v>
+        <v>13371061914.14</v>
       </c>
       <c r="G5" t="n">
-        <v>15544432776.39</v>
+        <v>20043174288.58</v>
       </c>
       <c r="H5" t="n">
-        <v>-1956621059.02</v>
+        <v>-3370273898.99</v>
       </c>
       <c r="I5" t="n">
-        <v>10798439626.08</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
+        <v>13371061914.14</v>
+      </c>
+      <c r="J5" t="n">
+        <v>7659506.28</v>
+      </c>
       <c r="K5" t="n">
-        <v>11654198814.4</v>
+        <v>14495690792.46</v>
       </c>
       <c r="L5" t="n">
-        <v>12352398814.4</v>
+        <v>18442519094.59</v>
       </c>
       <c r="M5" t="n">
-        <v>14052327254.27</v>
+        <v>19622258436.42</v>
       </c>
       <c r="N5" t="n">
-        <v>2398128439.87</v>
+        <v>5126567643.96</v>
       </c>
       <c r="O5" t="n">
-        <v>11654198814.4</v>
+        <v>14495690792.46</v>
       </c>
       <c r="P5" t="n">
-        <v>144011354.79</v>
+        <v>312768360</v>
       </c>
       <c r="Q5" t="n">
-        <v>7929949649.1</v>
+        <v>9858647154.799999</v>
       </c>
       <c r="R5" t="n">
-        <v>1494061855.4</v>
+        <v>375641474.73</v>
       </c>
       <c r="S5" t="n">
-        <v>3673412560</v>
+        <v>3739176560</v>
       </c>
       <c r="T5" t="n">
-        <v>3673412560</v>
+        <v>3739176560</v>
       </c>
       <c r="U5" t="n">
-        <v>12022542308.81</v>
+        <v>16253598422.88</v>
       </c>
       <c r="V5" t="n">
-        <v>977528591.2</v>
+        <v>6340400668.26</v>
       </c>
       <c r="W5" t="n">
-        <v>61374987.5</v>
+        <v>1271540187.25</v>
       </c>
       <c r="X5" t="n">
-        <v>143828977.22</v>
+        <v>1041981625.57</v>
       </c>
       <c r="Y5" t="n">
-        <v>67102341.77</v>
+        <v>60975543.7</v>
       </c>
       <c r="Z5" t="n">
-        <v>7022284.71</v>
+        <v>11415503.33</v>
       </c>
       <c r="AA5" t="n">
-        <v>698200000</v>
-      </c>
-      <c r="AB5" t="inlineStr"/>
+        <v>3954487808.41</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>7659506.28</v>
+      </c>
       <c r="AC5" t="n">
-        <v>698200000</v>
+        <v>3946828302.13</v>
       </c>
       <c r="AD5" t="n">
-        <v>11045013717.61</v>
+        <v>9913197754.620001</v>
       </c>
       <c r="AE5" t="n">
-        <v>64174144.35</v>
+        <v>130595616.84</v>
       </c>
       <c r="AF5" t="n">
-        <v>4694685647.83</v>
+        <v>4059394221.78</v>
       </c>
       <c r="AG5" t="n">
-        <v>3192033961.99</v>
+        <v>1600655193.99</v>
       </c>
       <c r="AH5" t="n">
-        <v>5630934171.75</v>
+        <v>4601791023.85</v>
       </c>
       <c r="AI5" t="n">
-        <v>2510348411.36</v>
+        <v>787354040.46</v>
       </c>
       <c r="AJ5" t="n">
-        <v>13132245.07</v>
+        <v>5184810.48</v>
       </c>
       <c r="AK5" t="n">
-        <v>230129660.47</v>
+        <v>121982504.27</v>
       </c>
       <c r="AL5" t="n">
-        <v>2877323854.85</v>
+        <v>3687269668.64</v>
       </c>
       <c r="AM5" t="n">
-        <v>26074869563.08</v>
+        <v>35875856859.3</v>
       </c>
       <c r="AN5" t="n">
-        <v>16986476904.49</v>
+        <v>29332933003.67</v>
       </c>
       <c r="AO5" t="n">
-        <v>1233474121.66</v>
+        <v>869175792.6</v>
       </c>
       <c r="AP5" t="n">
-        <v>46281332.08</v>
+        <v>391759394.84</v>
       </c>
       <c r="AQ5" t="n">
-        <v>35194274.66</v>
+        <v>97121574.92</v>
       </c>
       <c r="AR5" t="n">
-        <v>430366608.23</v>
+        <v>639478499.64</v>
       </c>
       <c r="AS5" t="n">
-        <v>430366608.23</v>
+        <v>639478499.64</v>
       </c>
       <c r="AT5" t="n">
-        <v>2290720357.68</v>
+        <v>4245631676.55</v>
       </c>
       <c r="AU5" t="n">
-        <v>251554318.49</v>
+        <v>383428384.26</v>
       </c>
       <c r="AV5" t="n">
-        <v>855759188.3200001</v>
+        <v>1124628878.32</v>
       </c>
       <c r="AW5" t="n">
-        <v>852612690.79</v>
+        <v>1121482380.79</v>
       </c>
       <c r="AX5" t="n">
         <v>3146497.53</v>
       </c>
       <c r="AY5" t="n">
-        <v>11824640100.94</v>
+        <v>21572279418.16</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-6358318380.78</v>
+        <v>-9206708633.1</v>
       </c>
       <c r="BA5" t="n">
-        <v>18182958481.72</v>
+        <v>30778988051.26</v>
       </c>
       <c r="BB5" t="n">
-        <v>1638316812.44</v>
+        <v>1784263208.99</v>
       </c>
       <c r="BC5" t="n">
-        <v>96021390.97</v>
+        <v>163865247.86</v>
       </c>
       <c r="BD5" t="n">
-        <v>10697438951.55</v>
+        <v>17618908576.86</v>
       </c>
       <c r="BE5" t="n">
-        <v>5751181326.76</v>
+        <v>11211951017.55</v>
       </c>
       <c r="BF5" t="n">
-        <v>9088392658.59</v>
+        <v>6542923855.63</v>
       </c>
       <c r="BG5" t="n">
-        <v>2009339665.15</v>
+        <v>1376306294.79</v>
       </c>
       <c r="BH5" t="n">
-        <v>98669716.73999999</v>
+        <v>89049811.15000001</v>
       </c>
       <c r="BI5" t="n">
-        <v>675611266.59</v>
+        <v>772352416.08</v>
       </c>
       <c r="BJ5" t="n">
         <v>0</v>
       </c>
       <c r="BK5" t="inlineStr"/>
       <c r="BL5" t="n">
-        <v>453485762.82</v>
+        <v>368374748.49</v>
       </c>
       <c r="BM5" t="n">
-        <v>222125503.77</v>
+        <v>403977667.59</v>
       </c>
       <c r="BN5" t="n">
-        <v>1341413121.84</v>
+        <v>289106557.87</v>
       </c>
       <c r="BO5" t="n">
-        <v>98170862.67</v>
+        <v>50636520.76</v>
       </c>
       <c r="BP5" t="n">
-        <v>-10755938.6</v>
+        <v>-4316253.27</v>
       </c>
       <c r="BQ5" t="n">
-        <v>108926801.27</v>
+        <v>54952774.03</v>
       </c>
       <c r="BR5" t="n">
-        <v>4865188025.6</v>
-      </c>
-      <c r="BS5" t="inlineStr"/>
+        <v>3965472254.98</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>165688622.53</v>
+      </c>
       <c r="BT5" t="n">
-        <v>4865188025.6</v>
+        <v>3799783632.45</v>
       </c>
       <c r="BU5" t="n">
-        <v>464271754.64</v>
+        <v>126983574.34</v>
       </c>
       <c r="BV5" t="n">
-        <v>3863639481.92</v>
+        <v>3672800058.11</v>
       </c>
     </row>
   </sheetData>
@@ -2842,576 +2842,576 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>3168021169.7</v>
+        <v>1670792146.5</v>
       </c>
       <c r="C2" t="n">
-        <v>-3772121057.86</v>
+        <v>-3710840222.22</v>
       </c>
       <c r="D2" t="n">
-        <v>3063927157.2</v>
+        <v>3237900000</v>
       </c>
       <c r="E2" t="n">
-        <v>-1338664002.89</v>
+        <v>-1811677969.57</v>
       </c>
       <c r="F2" t="n">
-        <v>3564320804.88</v>
+        <v>4198673766.97</v>
       </c>
       <c r="G2" t="n">
-        <v>3271471769.7</v>
+        <v>1180172242.6</v>
       </c>
       <c r="H2" t="n">
-        <v>2294532.85</v>
+        <v>1512338.31</v>
       </c>
       <c r="I2" t="n">
-        <v>290554502.33</v>
+        <v>3016989186.06</v>
       </c>
       <c r="J2" t="n">
-        <v>-2896754928.38</v>
+        <v>-2724019378.77</v>
       </c>
       <c r="K2" t="n">
-        <v>-522742809.46</v>
+        <v>-2028626610.63</v>
       </c>
       <c r="L2" t="n">
-        <v>-1313849053.06</v>
+        <v>-176477610.34</v>
       </c>
       <c r="M2" t="n">
-        <v>-708193900.66</v>
+        <v>-472940222.22</v>
       </c>
       <c r="N2" t="n">
-        <v>-708193900.66</v>
+        <v>-472940222.22</v>
       </c>
       <c r="O2" t="n">
-        <v>-3772121057.86</v>
+        <v>-3710840222.22</v>
       </c>
       <c r="P2" t="n">
-        <v>3063927157.2</v>
+        <v>3237900000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1319375741.88</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
+        <v>2258538448.76</v>
+      </c>
+      <c r="R2" t="n">
+        <v>13699.71</v>
+      </c>
       <c r="S2" t="n">
-        <v>-155266634.3</v>
+        <v>-37940213.75</v>
       </c>
       <c r="T2" t="n">
-        <v>69935146.52</v>
+        <v>1165876.18</v>
       </c>
       <c r="U2" t="n">
-        <v>-225201780.82</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+        <v>-39106089.93</v>
+      </c>
+      <c r="V2" t="n">
+        <v>4100005447.9</v>
+      </c>
+      <c r="W2" t="n">
+        <v>4100005447.9</v>
+      </c>
       <c r="X2" t="n">
-        <v>-1164109107.58</v>
+        <v>-1803540485.1</v>
       </c>
       <c r="Y2" t="n">
-        <v>174554895.31</v>
+        <v>8137484.47</v>
       </c>
       <c r="Z2" t="n">
-        <v>-1338664002.89</v>
+        <v>-1811677969.57</v>
       </c>
       <c r="AA2" t="n">
-        <v>4506685172.59</v>
+        <v>3482470116.07</v>
       </c>
       <c r="AB2" t="n">
-        <v>-235625649.84</v>
+        <v>-386170651.35</v>
       </c>
       <c r="AC2" t="n">
-        <v>-26722913.95</v>
+        <v>38550684.81</v>
       </c>
       <c r="AD2" t="n">
-        <v>644077711.85</v>
+        <v>-21733211.24</v>
       </c>
       <c r="AE2" t="n">
-        <v>-240618405.2</v>
+        <v>-277651359.66</v>
       </c>
       <c r="AF2" t="n">
-        <v>-612362042.54</v>
+        <v>-125336765.26</v>
       </c>
       <c r="AG2" t="n">
-        <v>439299625.79</v>
+        <v>269736833.86</v>
       </c>
       <c r="AH2" t="n">
-        <v>1482080875.38</v>
+        <v>1092010840.93</v>
       </c>
       <c r="AI2" t="n">
-        <v>126156637.66</v>
+        <v>77724952.89</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1355924237.72</v>
+        <v>1014285888.04</v>
       </c>
       <c r="AK2" t="n">
-        <v>-390159191.6</v>
+        <v>-3753269736.11</v>
       </c>
       <c r="AL2" t="n">
-        <v>14684727.3</v>
+        <v>551149984.8200001</v>
       </c>
       <c r="AM2" t="n">
-        <v>2873656833.7</v>
+        <v>5678478038.08</v>
       </c>
       <c r="AN2" t="n">
-        <v>4506685172.59</v>
+        <v>3482470116.07</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1191483767.46</v>
+        <v>-1290238679.66</v>
       </c>
       <c r="AP2" t="n">
-        <v>-7868702882.48</v>
+        <v>-8174301391.23</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-692358129.88</v>
+        <v>-512383820.27</v>
       </c>
       <c r="AR2" t="n">
-        <v>-782478055.9400001</v>
+        <v>-633529001.72</v>
       </c>
       <c r="AS2" t="n">
-        <v>-6393866696.66</v>
+        <v>-7028388569.24</v>
       </c>
       <c r="AT2" t="n">
-        <v>13566871822.53</v>
+        <v>12947010186.96</v>
       </c>
       <c r="AU2" t="n">
-        <v>141359567.45</v>
+        <v>126314166.61</v>
       </c>
       <c r="AV2" t="n">
-        <v>13425512255.08</v>
+        <v>12820696020.35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-539978531.89</v>
+        <v>-22784815.5</v>
       </c>
       <c r="C3" t="n">
-        <v>-2724454720.09</v>
+        <v>-4685397609.16</v>
       </c>
       <c r="D3" t="n">
-        <v>5155030584.39</v>
+        <v>5432931002.19</v>
       </c>
       <c r="E3" t="n">
-        <v>-3680482262.85</v>
+        <v>-3272420067.66</v>
       </c>
       <c r="F3" t="n">
-        <v>3271471769.7</v>
+        <v>1856784022.29</v>
       </c>
       <c r="G3" t="n">
-        <v>1856784022.29</v>
+        <v>4198673766.97</v>
       </c>
       <c r="H3" t="n">
-        <v>2907.03</v>
+        <v>145343.1</v>
       </c>
       <c r="I3" t="n">
-        <v>1414684840.38</v>
+        <v>-2342035087.78</v>
       </c>
       <c r="J3" t="n">
-        <v>1890346847.37</v>
+        <v>-2250503712.4</v>
       </c>
       <c r="K3" t="n">
-        <v>419162766.83</v>
+        <v>-2176111737.67</v>
       </c>
       <c r="L3" t="n">
-        <v>-806985682.8200001</v>
+        <v>-622742223.63</v>
       </c>
       <c r="M3" t="n">
-        <v>2430575864.3</v>
+        <v>747533393.03</v>
       </c>
       <c r="N3" t="n">
-        <v>2430575864.3</v>
+        <v>747533393.03</v>
       </c>
       <c r="O3" t="n">
-        <v>-2724454720.09</v>
+        <v>-4685397609.16</v>
       </c>
       <c r="P3" t="n">
-        <v>5155030584.39</v>
+        <v>5432931002.19</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3616165737.95</v>
+        <v>-3341166627.54</v>
       </c>
       <c r="R3" t="n">
-        <v>18542081.18</v>
+        <v>-25290689.13</v>
       </c>
       <c r="S3" t="n">
-        <v>42811378.11</v>
+        <v>-216337648.39</v>
       </c>
       <c r="T3" t="n">
-        <v>197811378.11</v>
+        <v>231579562.4</v>
       </c>
       <c r="U3" t="n">
-        <v>-155000000</v>
-      </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
+        <v>-447917210.79</v>
+      </c>
+      <c r="V3" t="n">
+        <v>164986616.68</v>
+      </c>
+      <c r="W3" t="n">
+        <v>164986616.68</v>
+      </c>
       <c r="X3" t="n">
-        <v>-3677519197.24</v>
+        <v>-3264524906.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>2963065.61</v>
+        <v>7895160.96</v>
       </c>
       <c r="Z3" t="n">
-        <v>-3680482262.85</v>
+        <v>-3272420067.66</v>
       </c>
       <c r="AA3" t="n">
-        <v>3140503730.96</v>
+        <v>3249635252.16</v>
       </c>
       <c r="AB3" t="n">
-        <v>83453458.14</v>
+        <v>-381116011.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>-12677360.35</v>
+        <v>-22526578.69</v>
       </c>
       <c r="AD3" t="n">
-        <v>175961434.86</v>
+        <v>-139860442.57</v>
       </c>
       <c r="AE3" t="n">
-        <v>241432222.79</v>
+        <v>-100643071.2</v>
       </c>
       <c r="AF3" t="n">
-        <v>-321262839.16</v>
+        <v>-118085919.24</v>
       </c>
       <c r="AG3" t="n">
-        <v>340611575.79</v>
+        <v>251763988.11</v>
       </c>
       <c r="AH3" t="n">
-        <v>1047346025.38</v>
+        <v>879681488.16</v>
       </c>
       <c r="AI3" t="n">
-        <v>89080685.83</v>
+        <v>53813918.78</v>
       </c>
       <c r="AJ3" t="n">
-        <v>958265339.55</v>
+        <v>825867569.38</v>
       </c>
       <c r="AK3" t="n">
-        <v>-542997367.4400001</v>
+        <v>-769218436.0700001</v>
       </c>
       <c r="AL3" t="n">
-        <v>7747946.36</v>
+        <v>44647341.71</v>
       </c>
       <c r="AM3" t="n">
-        <v>2143831928.33</v>
+        <v>3190111699.81</v>
       </c>
       <c r="AN3" t="n">
-        <v>3140503730.96</v>
+        <v>3249635252.16</v>
       </c>
       <c r="AO3" t="n">
-        <v>-1334950058.09</v>
+        <v>-773158383.4400001</v>
       </c>
       <c r="AP3" t="n">
-        <v>-6071582527.22</v>
+        <v>-5923163134.52</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-505741994.15</v>
+        <v>-356932710.04</v>
       </c>
       <c r="AR3" t="n">
-        <v>-827796439.67</v>
+        <v>-619339139.97</v>
       </c>
       <c r="AS3" t="n">
-        <v>-4738044093.4</v>
+        <v>-4946891284.51</v>
       </c>
       <c r="AT3" t="n">
-        <v>10547036316.27</v>
+        <v>9945956770.120001</v>
       </c>
       <c r="AU3" t="n">
-        <v>111930921.96</v>
+        <v>137675139.07</v>
       </c>
       <c r="AV3" t="n">
-        <v>10435105394.31</v>
+        <v>9808281631.049999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-22784815.5</v>
+        <v>-539978531.89</v>
       </c>
       <c r="C4" t="n">
-        <v>-4685397609.16</v>
+        <v>-2724454720.09</v>
       </c>
       <c r="D4" t="n">
-        <v>5432931002.19</v>
+        <v>5155030584.39</v>
       </c>
       <c r="E4" t="n">
-        <v>-3272420067.66</v>
+        <v>-3680482262.85</v>
       </c>
       <c r="F4" t="n">
+        <v>3271471769.7</v>
+      </c>
+      <c r="G4" t="n">
         <v>1856784022.29</v>
       </c>
-      <c r="G4" t="n">
-        <v>4198673766.97</v>
-      </c>
       <c r="H4" t="n">
-        <v>145343.1</v>
+        <v>2907.03</v>
       </c>
       <c r="I4" t="n">
-        <v>-2342035087.78</v>
+        <v>1414684840.38</v>
       </c>
       <c r="J4" t="n">
-        <v>-2250503712.4</v>
+        <v>1890346847.37</v>
       </c>
       <c r="K4" t="n">
-        <v>-2176111737.67</v>
+        <v>419162766.83</v>
       </c>
       <c r="L4" t="n">
-        <v>-622742223.63</v>
+        <v>-806985682.8200001</v>
       </c>
       <c r="M4" t="n">
-        <v>747533393.03</v>
+        <v>2430575864.3</v>
       </c>
       <c r="N4" t="n">
-        <v>747533393.03</v>
+        <v>2430575864.3</v>
       </c>
       <c r="O4" t="n">
-        <v>-4685397609.16</v>
+        <v>-2724454720.09</v>
       </c>
       <c r="P4" t="n">
-        <v>5432931002.19</v>
+        <v>5155030584.39</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3341166627.54</v>
+        <v>-3616165737.95</v>
       </c>
       <c r="R4" t="n">
-        <v>-25290689.13</v>
+        <v>18542081.18</v>
       </c>
       <c r="S4" t="n">
-        <v>-216337648.39</v>
+        <v>42811378.11</v>
       </c>
       <c r="T4" t="n">
-        <v>231579562.4</v>
+        <v>197811378.11</v>
       </c>
       <c r="U4" t="n">
-        <v>-447917210.79</v>
-      </c>
-      <c r="V4" t="n">
-        <v>164986616.68</v>
-      </c>
-      <c r="W4" t="n">
-        <v>164986616.68</v>
-      </c>
+        <v>-155000000</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>-3264524906.7</v>
+        <v>-3677519197.24</v>
       </c>
       <c r="Y4" t="n">
-        <v>7895160.96</v>
+        <v>2963065.61</v>
       </c>
       <c r="Z4" t="n">
-        <v>-3272420067.66</v>
+        <v>-3680482262.85</v>
       </c>
       <c r="AA4" t="n">
-        <v>3249635252.16</v>
+        <v>3140503730.96</v>
       </c>
       <c r="AB4" t="n">
-        <v>-381116011.7</v>
+        <v>83453458.14</v>
       </c>
       <c r="AC4" t="n">
-        <v>-22526578.69</v>
+        <v>-12677360.35</v>
       </c>
       <c r="AD4" t="n">
-        <v>-139860442.57</v>
+        <v>175961434.86</v>
       </c>
       <c r="AE4" t="n">
-        <v>-100643071.2</v>
+        <v>241432222.79</v>
       </c>
       <c r="AF4" t="n">
-        <v>-118085919.24</v>
+        <v>-321262839.16</v>
       </c>
       <c r="AG4" t="n">
-        <v>251763988.11</v>
+        <v>340611575.79</v>
       </c>
       <c r="AH4" t="n">
-        <v>879681488.16</v>
+        <v>1047346025.38</v>
       </c>
       <c r="AI4" t="n">
-        <v>53813918.78</v>
+        <v>89080685.83</v>
       </c>
       <c r="AJ4" t="n">
-        <v>825867569.38</v>
+        <v>958265339.55</v>
       </c>
       <c r="AK4" t="n">
-        <v>-769218436.0700001</v>
+        <v>-542997367.4400001</v>
       </c>
       <c r="AL4" t="n">
-        <v>44647341.71</v>
+        <v>7747946.36</v>
       </c>
       <c r="AM4" t="n">
-        <v>3190111699.81</v>
+        <v>2143831928.33</v>
       </c>
       <c r="AN4" t="n">
-        <v>3249635252.16</v>
+        <v>3140503730.96</v>
       </c>
       <c r="AO4" t="n">
-        <v>-773158383.4400001</v>
+        <v>-1334950058.09</v>
       </c>
       <c r="AP4" t="n">
-        <v>-5923163134.52</v>
+        <v>-6071582527.22</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-356932710.04</v>
+        <v>-505741994.15</v>
       </c>
       <c r="AR4" t="n">
-        <v>-619339139.97</v>
+        <v>-827796439.67</v>
       </c>
       <c r="AS4" t="n">
-        <v>-4946891284.51</v>
+        <v>-4738044093.4</v>
       </c>
       <c r="AT4" t="n">
-        <v>9945956770.120001</v>
+        <v>10547036316.27</v>
       </c>
       <c r="AU4" t="n">
-        <v>137675139.07</v>
+        <v>111930921.96</v>
       </c>
       <c r="AV4" t="n">
-        <v>9808281631.049999</v>
+        <v>10435105394.31</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>1670792146.5</v>
+        <v>3168021169.7</v>
       </c>
       <c r="C5" t="n">
-        <v>-3710840222.22</v>
+        <v>-3772121057.86</v>
       </c>
       <c r="D5" t="n">
-        <v>3237900000</v>
+        <v>3063927157.2</v>
       </c>
       <c r="E5" t="n">
-        <v>-1811677969.57</v>
+        <v>-1338664002.89</v>
       </c>
       <c r="F5" t="n">
-        <v>4198673766.97</v>
+        <v>3564320804.88</v>
       </c>
       <c r="G5" t="n">
-        <v>1180172242.6</v>
+        <v>3271471769.7</v>
       </c>
       <c r="H5" t="n">
-        <v>1512338.31</v>
+        <v>2294532.85</v>
       </c>
       <c r="I5" t="n">
-        <v>3016989186.06</v>
+        <v>290554502.33</v>
       </c>
       <c r="J5" t="n">
-        <v>-2724019378.77</v>
+        <v>-2896754928.38</v>
       </c>
       <c r="K5" t="n">
-        <v>-2028626610.63</v>
+        <v>-522742809.46</v>
       </c>
       <c r="L5" t="n">
-        <v>-176477610.34</v>
+        <v>-1313849053.06</v>
       </c>
       <c r="M5" t="n">
-        <v>-472940222.22</v>
+        <v>-708193900.66</v>
       </c>
       <c r="N5" t="n">
-        <v>-472940222.22</v>
+        <v>-708193900.66</v>
       </c>
       <c r="O5" t="n">
-        <v>-3710840222.22</v>
+        <v>-3772121057.86</v>
       </c>
       <c r="P5" t="n">
-        <v>3237900000</v>
+        <v>3063927157.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>2258538448.76</v>
-      </c>
-      <c r="R5" t="n">
-        <v>13699.71</v>
-      </c>
+        <v>-1319375741.88</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>-37940213.75</v>
+        <v>-155266634.3</v>
       </c>
       <c r="T5" t="n">
-        <v>1165876.18</v>
+        <v>69935146.52</v>
       </c>
       <c r="U5" t="n">
-        <v>-39106089.93</v>
-      </c>
-      <c r="V5" t="n">
-        <v>4100005447.9</v>
-      </c>
-      <c r="W5" t="n">
-        <v>4100005447.9</v>
-      </c>
+        <v>-225201780.82</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>-1803540485.1</v>
+        <v>-1164109107.58</v>
       </c>
       <c r="Y5" t="n">
-        <v>8137484.47</v>
+        <v>174554895.31</v>
       </c>
       <c r="Z5" t="n">
-        <v>-1811677969.57</v>
+        <v>-1338664002.89</v>
       </c>
       <c r="AA5" t="n">
-        <v>3482470116.07</v>
+        <v>4506685172.59</v>
       </c>
       <c r="AB5" t="n">
-        <v>-386170651.35</v>
+        <v>-235625649.84</v>
       </c>
       <c r="AC5" t="n">
-        <v>38550684.81</v>
+        <v>-26722913.95</v>
       </c>
       <c r="AD5" t="n">
-        <v>-21733211.24</v>
+        <v>644077711.85</v>
       </c>
       <c r="AE5" t="n">
-        <v>-277651359.66</v>
+        <v>-240618405.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>-125336765.26</v>
+        <v>-612362042.54</v>
       </c>
       <c r="AG5" t="n">
-        <v>269736833.86</v>
+        <v>439299625.79</v>
       </c>
       <c r="AH5" t="n">
-        <v>1092010840.93</v>
+        <v>1482080875.38</v>
       </c>
       <c r="AI5" t="n">
-        <v>77724952.89</v>
+        <v>126156637.66</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1014285888.04</v>
+        <v>1355924237.72</v>
       </c>
       <c r="AK5" t="n">
-        <v>-3753269736.11</v>
+        <v>-390159191.6</v>
       </c>
       <c r="AL5" t="n">
-        <v>551149984.8200001</v>
+        <v>14684727.3</v>
       </c>
       <c r="AM5" t="n">
-        <v>5678478038.08</v>
+        <v>2873656833.7</v>
       </c>
       <c r="AN5" t="n">
-        <v>3482470116.07</v>
+        <v>4506685172.59</v>
       </c>
       <c r="AO5" t="n">
-        <v>-1290238679.66</v>
+        <v>-1191483767.46</v>
       </c>
       <c r="AP5" t="n">
-        <v>-8174301391.23</v>
+        <v>-7868702882.48</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-512383820.27</v>
+        <v>-692358129.88</v>
       </c>
       <c r="AR5" t="n">
-        <v>-633529001.72</v>
+        <v>-782478055.9400001</v>
       </c>
       <c r="AS5" t="n">
-        <v>-7028388569.24</v>
+        <v>-6393866696.66</v>
       </c>
       <c r="AT5" t="n">
-        <v>12947010186.96</v>
+        <v>13566871822.53</v>
       </c>
       <c r="AU5" t="n">
-        <v>126314166.61</v>
+        <v>141359567.45</v>
       </c>
       <c r="AV5" t="n">
-        <v>12820696020.35</v>
+        <v>13425512255.08</v>
       </c>
     </row>
   </sheetData>
@@ -3425,7 +3425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EZ2"/>
+  <dimension ref="A1:FB2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3866,345 +3866,355 @@
       </c>
       <c r="CJ1" t="inlineStr">
         <is>
+          <t>recommendationMean</t>
+        </is>
+      </c>
+      <c r="CK1" t="inlineStr">
+        <is>
           <t>recommendationKey</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>numberOfAnalystOpinions</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>totalCash</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>totalCashPerShare</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>totalDebt</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>quickRatio</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>currentRatio</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>totalRevenue</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>debtToEquity</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>revenuePerShare</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>returnOnAssets</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>returnOnEquity</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>grossProfits</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>freeCashflow</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>operatingCashflow</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>earningsGrowth</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>revenueGrowth</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>grossMargins</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>ebitdaMargins</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>operatingMargins</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>financialCurrency</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>symbol</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>typeDisp</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>quoteSourceName</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>triggerable</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>customPriceAlertConfidence</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="EE1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="EF1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="EG1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="EH1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="EI1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="EJ1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="EK1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="EL1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="EM1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="EN1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="EO1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="EP1" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>epsForward</t>
         </is>
       </c>
-      <c r="EQ1" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>epsCurrentYear</t>
         </is>
       </c>
-      <c r="ER1" t="inlineStr">
+      <c r="ES1" t="inlineStr">
+        <is>
+          <t>priceEpsCurrentYear</t>
+        </is>
+      </c>
+      <c r="ET1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="ES1" t="inlineStr">
+      <c r="EU1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="ET1" t="inlineStr">
+      <c r="EV1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="EU1" t="inlineStr">
+      <c r="EW1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EV1" t="inlineStr">
+      <c r="EX1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="EW1" t="inlineStr">
+      <c r="EY1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="EX1" t="inlineStr">
-        <is>
-          <t>priceEpsCurrentYear</t>
-        </is>
-      </c>
-      <c r="EY1" t="inlineStr">
+      <c r="EZ1" t="inlineStr">
+        <is>
+          <t>averageAnalystRating</t>
+        </is>
+      </c>
+      <c r="FA1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="EZ1" t="inlineStr">
+      <c r="FB1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -4291,7 +4301,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Yuhu  Ji', 'age': 51, 'title': 'Deputy GM &amp; Director', 'yearBorn': 1974, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yanhua  Wang', 'age': 48, 'title': 'Chief Engineer', 'yearBorn': 1977, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yang  Hua', 'age': 48, 'title': 'Deputy GM &amp; Board Secretary', 'yearBorn': 1977, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yuan  Gao', 'age': 47, 'title': 'Deputy General Manager', 'yearBorn': 1978, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Zhanfei  Xing', 'age': 52, 'title': 'GM &amp; Director', 'yearBorn': 1973, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jun  Li', 'age': 38, 'title': 'Financial Director', 'yearBorn': 1987, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yu Ying  Ma', 'age': 46, 'title': 'Chief Accountant', 'yearBorn': 1979, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Xiang  Lu', 'age': 53, 'title': 'Head of Internal Control', 'yearBorn': 1972, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Jiawei  Wang', 'title': 'Board Secretary', 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Peng Cheng  Dai', 'age': 41, 'title': 'Deputy General Manager', 'yearBorn': 1984, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -4306,34 +4316,34 @@
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>7.22</v>
+        <v>6.29</v>
       </c>
       <c r="V2" t="n">
-        <v>7.47</v>
+        <v>6.56</v>
       </c>
       <c r="W2" t="n">
-        <v>7.13</v>
+        <v>6.17</v>
       </c>
       <c r="X2" t="n">
-        <v>7.35</v>
+        <v>6.57</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.22</v>
+        <v>6.29</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.47</v>
+        <v>6.56</v>
       </c>
       <c r="AA2" t="n">
-        <v>7.13</v>
+        <v>6.17</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.35</v>
+        <v>6.57</v>
       </c>
       <c r="AC2" t="n">
         <v>0.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>4.17</v>
+        <v>4.42</v>
       </c>
       <c r="AE2" t="n">
         <v>1750118400</v>
@@ -4342,34 +4352,34 @@
         <v>1.1111</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.727</v>
+        <v>0.539</v>
       </c>
       <c r="AH2" t="n">
-        <v>26.666664</v>
+        <v>24.185184</v>
       </c>
       <c r="AI2" t="n">
-        <v>11.076923</v>
+        <v>10.046155</v>
       </c>
       <c r="AJ2" t="n">
-        <v>41867009</v>
+        <v>150169463</v>
       </c>
       <c r="AK2" t="n">
-        <v>41867009</v>
+        <v>150169463</v>
       </c>
       <c r="AL2" t="n">
-        <v>50032212</v>
+        <v>45275164</v>
       </c>
       <c r="AM2" t="n">
-        <v>42801008</v>
+        <v>57121420</v>
       </c>
       <c r="AN2" t="n">
-        <v>42801008</v>
+        <v>57121420</v>
       </c>
       <c r="AO2" t="n">
-        <v>7.19</v>
+        <v>6.49</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>0</v>
@@ -4378,10 +4388,10 @@
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>26761185280</v>
+        <v>24270909440</v>
       </c>
       <c r="AT2" t="n">
-        <v>26761187232</v>
+        <v>23378870512</v>
       </c>
       <c r="AU2" t="n">
         <v>4.72</v>
@@ -4396,19 +4406,19 @@
         <v>0.703703</v>
       </c>
       <c r="AY2" t="n">
-        <v>2.2442935</v>
+        <v>2.0354495</v>
       </c>
       <c r="AZ2" t="n">
-        <v>8.423</v>
+        <v>7.9666</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.63055</v>
+        <v>7.66</v>
       </c>
       <c r="BB2" t="n">
         <v>0.3</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.04155125</v>
+        <v>0.047694758</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -4419,7 +4429,7 @@
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>43103387648</v>
+        <v>40544649216</v>
       </c>
       <c r="BG2" t="n">
         <v>0.0858</v>
@@ -4434,7 +4444,7 @@
         <v>0.31847998</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.21327</v>
+        <v>0.21172</v>
       </c>
       <c r="BL2" t="n">
         <v>3716831560</v>
@@ -4443,7 +4453,7 @@
         <v>3.41</v>
       </c>
       <c r="BN2" t="n">
-        <v>2.1114368</v>
+        <v>1.914956</v>
       </c>
       <c r="BO2" t="n">
         <v>1767139200</v>
@@ -4475,16 +4485,16 @@
         <v>1463011200</v>
       </c>
       <c r="BX2" t="n">
-        <v>3.615</v>
+        <v>3.4</v>
       </c>
       <c r="BY2" t="n">
-        <v>10.881</v>
+        <v>10.235</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.42857146</v>
+        <v>0.32421052</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.27697718</v>
+        <v>0.24487448</v>
       </c>
       <c r="CB2" t="n">
         <v>0.3</v>
@@ -4498,7 +4508,7 @@
         </is>
       </c>
       <c r="CE2" t="n">
-        <v>7.2</v>
+        <v>6.53</v>
       </c>
       <c r="CF2" t="n">
         <v>10.5</v>
@@ -4512,251 +4522,259 @@
       <c r="CI2" t="n">
         <v>10.5</v>
       </c>
-      <c r="CJ2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="CK2" t="n">
+      <c r="CJ2" t="n">
         <v>1</v>
       </c>
+      <c r="CK2" t="inlineStr">
+        <is>
+          <t>strong_buy</t>
+        </is>
+      </c>
       <c r="CL2" t="n">
+        <v>2</v>
+      </c>
+      <c r="CM2" t="n">
         <v>1508298880</v>
       </c>
-      <c r="CM2" t="n">
+      <c r="CN2" t="n">
         <v>0.395</v>
       </c>
-      <c r="CN2" t="n">
+      <c r="CO2" t="n">
         <v>3961260032</v>
       </c>
-      <c r="CO2" t="n">
+      <c r="CP2" t="n">
         <v>13177167872</v>
       </c>
-      <c r="CP2" t="n">
+      <c r="CQ2" t="n">
         <v>0.153</v>
       </c>
-      <c r="CQ2" t="n">
+      <c r="CR2" t="n">
         <v>0.346</v>
       </c>
-      <c r="CR2" t="n">
+      <c r="CS2" t="n">
         <v>11924103168</v>
       </c>
-      <c r="CS2" t="n">
+      <c r="CT2" t="n">
         <v>77.68899999999999</v>
       </c>
-      <c r="CT2" t="n">
+      <c r="CU2" t="n">
         <v>3.218</v>
       </c>
-      <c r="CU2" t="n">
+      <c r="CV2" t="n">
         <v>0.037920002</v>
       </c>
-      <c r="CV2" t="n">
+      <c r="CW2" t="n">
         <v>0.08254</v>
       </c>
-      <c r="CW2" t="n">
+      <c r="CX2" t="n">
         <v>3618444032</v>
       </c>
-      <c r="CX2" t="n">
+      <c r="CY2" t="n">
         <v>2087036928</v>
       </c>
-      <c r="CY2" t="n">
+      <c r="CZ2" t="n">
         <v>2334821888</v>
       </c>
-      <c r="CZ2" t="n">
+      <c r="DA2" t="n">
         <v>0.222</v>
       </c>
-      <c r="DA2" t="n">
+      <c r="DB2" t="n">
         <v>-0.052</v>
       </c>
-      <c r="DB2" t="n">
+      <c r="DC2" t="n">
         <v>0.30346</v>
       </c>
-      <c r="DC2" t="n">
+      <c r="DD2" t="n">
         <v>0.33221</v>
       </c>
-      <c r="DD2" t="n">
+      <c r="DE2" t="n">
         <v>0.21697001</v>
       </c>
-      <c r="DE2" t="inlineStr">
+      <c r="DF2" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="DF2" t="inlineStr">
+      <c r="DG2" t="inlineStr">
         <is>
           <t>000683.SZ</t>
         </is>
       </c>
-      <c r="DG2" t="inlineStr">
+      <c r="DH2" t="inlineStr">
         <is>
           <t>en-US</t>
         </is>
       </c>
-      <c r="DH2" t="inlineStr">
+      <c r="DI2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="DI2" t="inlineStr">
+      <c r="DJ2" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="DJ2" t="inlineStr">
+      <c r="DK2" t="inlineStr">
         <is>
           <t>Delayed Quote</t>
         </is>
       </c>
-      <c r="DK2" t="b">
+      <c r="DL2" t="b">
         <v>0</v>
       </c>
-      <c r="DL2" t="inlineStr">
+      <c r="DM2" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="DM2" t="inlineStr">
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>SHZ</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>finmb_6480331</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>Asia/Shanghai</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>CST</t>
+        </is>
+      </c>
+      <c r="DR2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>cn_market</t>
+        </is>
+      </c>
+      <c r="DT2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>3.8155842</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DX2" t="n">
+        <v>1782111873</v>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="DZ2" t="inlineStr">
         <is>
           <t>INNER MONGOLIA BERUN CHEMICAL C</t>
         </is>
       </c>
-      <c r="DN2" t="inlineStr">
+      <c r="EA2" t="inlineStr">
         <is>
           <t>Inner Mongolia Berun Chemical Company Limited</t>
         </is>
       </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DP2" t="n">
-        <v>1780038297</v>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>SHZ</t>
-        </is>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>finmb_6480331</t>
-        </is>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>Asia/Shanghai</t>
-        </is>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>CST</t>
-        </is>
-      </c>
-      <c r="DU2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>cn_market</t>
-        </is>
-      </c>
-      <c r="DW2" t="b">
+      <c r="EB2" t="b">
         <v>0</v>
       </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="DY2" t="n">
-        <v>-0.27700806</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="EA2" t="b">
+      <c r="EC2" t="n">
+        <v>854674200000</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>0.24000025</v>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>6.17 - 6.57</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>Shenzhen</t>
+        </is>
+      </c>
+      <c r="EG2" t="n">
+        <v>45275164</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>1.8100004</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>0.38347468</v>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>4.72 - 10.0</t>
+        </is>
+      </c>
+      <c r="EK2" t="n">
+        <v>-3.4699998</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>-0.34699997</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>32.42105</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>1651143540</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>1651233600</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>11.872727</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>-1.4365997</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>-0.18032783</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>-1.1299996</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>-0.14751954</v>
+      </c>
+      <c r="EX2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EZ2" t="inlineStr">
+        <is>
+          <t>1.0 - Strong Buy</t>
+        </is>
+      </c>
+      <c r="FA2" t="b">
         <v>0</v>
       </c>
-      <c r="EB2" t="n">
-        <v>854674200000</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>-0.01999998</v>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>7.13 - 7.35</t>
-        </is>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>Shenzhen</t>
-        </is>
-      </c>
-      <c r="EF2" t="n">
-        <v>50032212</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>0.52542377</v>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>4.72 - 10.0</t>
-        </is>
-      </c>
-      <c r="EJ2" t="n">
-        <v>-2.8000002</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>-0.28000003</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>42.857147</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>1651143540</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>1651233600</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="EQ2" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="ER2" t="n">
-        <v>-1.2230005</v>
-      </c>
-      <c r="ES2" t="n">
-        <v>-0.14519773</v>
-      </c>
-      <c r="ET2" t="n">
-        <v>-0.4305501</v>
-      </c>
-      <c r="EU2" t="n">
-        <v>-0.056424517</v>
-      </c>
-      <c r="EV2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EW2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EX2" t="n">
-        <v>13.090908</v>
-      </c>
-      <c r="EY2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EZ2" t="inlineStr"/>
+      <c r="FB2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
